--- a/data/raw_data.xlsx
+++ b/data/raw_data.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H282"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6300,9 +6300,383 @@
         <v>42736</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>2025-10-14T00:04:15.000</v>
+      </c>
+      <c r="C261" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D261" t="str">
+        <v>18.090999999999998</v>
+      </c>
+      <c r="E261" t="str">
+        <v>0.0225</v>
+      </c>
+      <c r="F261" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>2025-10-14T00:11:13.000</v>
+      </c>
+      <c r="C262" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D262" t="str">
+        <v>17.8274</v>
+      </c>
+      <c r="E262" t="str">
+        <v>0.0374</v>
+      </c>
+      <c r="F262" t="str">
+        <v>r</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>2025-10-14T00:04:22.000</v>
+      </c>
+      <c r="C263" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D263" t="str">
+        <v>17.3029</v>
+      </c>
+      <c r="E263" t="str">
+        <v>0.0659</v>
+      </c>
+      <c r="F263" t="str">
+        <v>i</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>2025-10-14T00:11:08.000</v>
+      </c>
+      <c r="C264" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D264" t="str">
+        <v>18.6177</v>
+      </c>
+      <c r="E264" t="str">
+        <v>0.1533</v>
+      </c>
+      <c r="F264" t="str">
+        <v>m400</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>2025-10-14T00:11:15.000</v>
+      </c>
+      <c r="C265" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D265" t="str">
+        <v>18.2558</v>
+      </c>
+      <c r="E265" t="str">
+        <v>0.0715</v>
+      </c>
+      <c r="F265" t="str">
+        <v>m425</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>2025-10-14T00:04:10.000</v>
+      </c>
+      <c r="C266" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D266" t="str">
+        <v>18.0339</v>
+      </c>
+      <c r="E266" t="str">
+        <v>0.0583</v>
+      </c>
+      <c r="F266" t="str">
+        <v>m450</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>2025-10-14T00:11:07.667</v>
+      </c>
+      <c r="C267" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D267" t="str">
+        <v>18.045499999999997</v>
+      </c>
+      <c r="E267" t="str">
+        <v>0.0552</v>
+      </c>
+      <c r="F267" t="str">
+        <v>m475</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>2025-10-14T00:11:52.000</v>
+      </c>
+      <c r="C268" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D268" t="str">
+        <v>18.2531</v>
+      </c>
+      <c r="E268" t="str">
+        <v>0.0623</v>
+      </c>
+      <c r="F268" t="str">
+        <v>m500</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>2025-10-14T00:11:09.000</v>
+      </c>
+      <c r="C269" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D269" t="str">
+        <v>17.8869</v>
+      </c>
+      <c r="E269" t="str">
+        <v>0.0483</v>
+      </c>
+      <c r="F269" t="str">
+        <v>m525</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>2025-10-14T00:11:14.667</v>
+      </c>
+      <c r="C270" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D270" t="str">
+        <v>17.8523</v>
+      </c>
+      <c r="E270" t="str">
+        <v>0.07</v>
+      </c>
+      <c r="F270" t="str">
+        <v>m550</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>2025-10-14T00:04:32.000</v>
+      </c>
+      <c r="C271" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D271" t="str">
+        <v>17.8886</v>
+      </c>
+      <c r="E271" t="str">
+        <v>0.0701</v>
+      </c>
+      <c r="F271" t="str">
+        <v>m575</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>2025-10-14T00:04:28.000</v>
+      </c>
+      <c r="C272" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D272" t="str">
+        <v>17.860400000000002</v>
+      </c>
+      <c r="E272" t="str">
+        <v>0.1003</v>
+      </c>
+      <c r="F272" t="str">
+        <v>m600</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>2025-10-14T00:04:18.000</v>
+      </c>
+      <c r="C273" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D273" t="str">
+        <v>17.6587</v>
+      </c>
+      <c r="E273" t="str">
+        <v>0.1052</v>
+      </c>
+      <c r="F273" t="str">
+        <v>m625</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>2025-10-14T00:04:09.000</v>
+      </c>
+      <c r="C274" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D274" t="str">
+        <v>17.5783</v>
+      </c>
+      <c r="E274" t="str">
+        <v>0.079</v>
+      </c>
+      <c r="F274" t="str">
+        <v>m650</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>2025-10-14T00:11:41.000</v>
+      </c>
+      <c r="C275" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D275" t="str">
+        <v>17.6936</v>
+      </c>
+      <c r="E275" t="str">
+        <v>0.0837</v>
+      </c>
+      <c r="F275" t="str">
+        <v>m675</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>2025-10-14T00:04:12.000</v>
+      </c>
+      <c r="C276" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D276" t="str">
+        <v>17.4843</v>
+      </c>
+      <c r="E276" t="str">
+        <v>0.0917</v>
+      </c>
+      <c r="F276" t="str">
+        <v>m700</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>2025-10-14T00:07:59.833</v>
+      </c>
+      <c r="C277" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D277" t="str">
+        <v>17.291800000000002</v>
+      </c>
+      <c r="E277" t="str">
+        <v>0.1273</v>
+      </c>
+      <c r="F277" t="str">
+        <v>m750</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>2025-10-14T00:11:03.000</v>
+      </c>
+      <c r="C278" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D278" t="str">
+        <v>17.30872064963861</v>
+      </c>
+      <c r="E278" t="str">
+        <v>0.22752352991813687</v>
+      </c>
+      <c r="F278" t="str">
+        <v>m775</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>2025-10-14T00:04:28.000</v>
+      </c>
+      <c r="C279" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D279" t="str">
+        <v>16.951810644960474</v>
+      </c>
+      <c r="E279" t="str">
+        <v>0.21101875222508443</v>
+      </c>
+      <c r="F279" t="str">
+        <v>m800</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>2025-10-14T00:11:40.000</v>
+      </c>
+      <c r="C280" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D280" t="str">
+        <v>17.51655798891263</v>
+      </c>
+      <c r="E280" t="str">
+        <v>0.3527597315123148</v>
+      </c>
+      <c r="F280" t="str">
+        <v>m825</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>2025-10-14T00:04:08.667</v>
+      </c>
+      <c r="C281" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D281" t="str">
+        <v>17.511639359722267</v>
+      </c>
+      <c r="E281" t="str">
+        <v>0.6164457444803931</v>
+      </c>
+      <c r="F281" t="str">
+        <v>m850</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>2025-10-14T00:07:38.167</v>
+      </c>
+      <c r="C282" t="str">
+        <v>7DT</v>
+      </c>
+      <c r="D282" t="str">
+        <v>16.88992912508132</v>
+      </c>
+      <c r="E282" t="str">
+        <v>0.4916548577615109</v>
+      </c>
+      <c r="F282" t="str">
+        <v>m875</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H260"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H282"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/raw_data.xlsx
+++ b/data/raw_data.xlsx
@@ -444,7 +444,7 @@
         <v xml:space="preserve">0.01 </v>
       </c>
       <c r="F2" t="str">
-        <v>B</v>
+        <v>Blue</v>
       </c>
       <c r="G2" t="str">
         <v>6*50 sec</v>
@@ -467,7 +467,7 @@
         <v xml:space="preserve">0.01 </v>
       </c>
       <c r="F3" t="str">
-        <v>R</v>
+        <v>Red</v>
       </c>
       <c r="G3" t="str">
         <v>6*50 sec</v>
